--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484045_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484045_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4724</v>
+        <v>2.3277</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1911</v>
+        <v>2.9903</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7187</v>
+        <v>-0.6626</v>
       </c>
       <c r="G2" t="n">
         <v>0.7703</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.0201</v>
+        <v>-1.1648</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4226</v>
+        <v>-0.6234</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5975</v>
+        <v>-0.5414</v>
       </c>
       <c r="V2" t="n">
         <v>1.1352</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. MARTÍN LLAVERÍA</t>
+          <t>E. NOGUES MARTIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1231</v>
+        <v>1.0909</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5982</v>
+        <v>3.0493</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5248</v>
+        <v>-1.9583</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.3937</v>
+        <v>1.5284</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1293</v>
+        <v>-2.1263</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2644</v>
+        <v>3.6547</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.08210000000000001</v>
+        <v>3.3055</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0658</v>
+        <v>0.208</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1479</v>
+        <v>3.0975</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3116</v>
+        <v>-1.7771</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.195</v>
+        <v>-2.3343</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1165</v>
+        <v>0.5572</v>
       </c>
       <c r="P3" t="n">
         <v>1.9838</v>
@@ -688,28 +688,28 @@
         <v>2.1822</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1957</v>
+        <v>-0.8063</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8787</v>
+        <v>-0.8558</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6831</v>
+        <v>0.0495</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3373</v>
+        <v>-1.615</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3373</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. NOGUES MARTIN</t>
+          <t>A. CRUZ JOBACHO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9127</v>
+        <v>0.6201</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6185</v>
+        <v>0.8834</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7058</v>
+        <v>-0.2633</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5284</v>
+        <v>0.6097</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.1263</v>
+        <v>0.3377</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6547</v>
+        <v>0.2721</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3055</v>
+        <v>1.0081</v>
       </c>
       <c r="K4" t="n">
-        <v>0.208</v>
+        <v>1.0081</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0975</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7771</v>
+        <v>-0.3983</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.3343</v>
+        <v>-0.6704</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5572</v>
+        <v>0.2721</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9838</v>
+        <v>0.3968</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1822</v>
+        <v>0.3968</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9846</v>
+        <v>-0.1205</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2865</v>
+        <v>-0.1247</v>
       </c>
       <c r="U4" t="n">
-        <v>0.302</v>
+        <v>0.0042</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.615</v>
+        <v>-0.266</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7979000000000001</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.4129</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CRUZ JOBACHO</t>
+          <t>L. MARTÍN LLAVERÍA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5359</v>
+        <v>0.3677</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8834</v>
+        <v>-0.2974</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3475</v>
+        <v>0.6651</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6097</v>
+        <v>-1.3937</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3377</v>
+        <v>-1.1293</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2721</v>
+        <v>-0.2644</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0081</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0081</v>
+        <v>0.0658</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.1479</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3983</v>
+        <v>-1.3116</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6704</v>
+        <v>-1.195</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2721</v>
+        <v>-0.1165</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3968</v>
+        <v>1.9838</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3968</v>
+        <v>2.1822</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2046</v>
+        <v>-0.5597</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1247</v>
+        <v>-0.0169</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0799</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.266</v>
+        <v>0.3373</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.266</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="6">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3591</v>
+        <v>-0.0709</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9445</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5853</v>
+        <v>0.6695</v>
       </c>
       <c r="G7" t="n">
         <v>0.9164</v>
@@ -1000,13 +1000,13 @@
         <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8111</v>
+        <v>-0.5229</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1133</v>
+        <v>0.0907</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6978</v>
+        <v>-0.6136</v>
       </c>
       <c r="V7" t="n">
         <v>-0.266</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ESONO MBA</t>
+          <t>M. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0194</v>
+        <v>-1.0625</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4984</v>
+        <v>0.574</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.521</v>
+        <v>-1.6365</v>
       </c>
       <c r="G8" t="n">
-        <v>2.645</v>
+        <v>2.0972</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0762</v>
+        <v>-1.2804</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5688</v>
+        <v>3.3775</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3583</v>
+        <v>3.0792</v>
       </c>
       <c r="K8" t="n">
-        <v>2.1976</v>
+        <v>0.3884</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1606</v>
+        <v>2.6908</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2867</v>
+        <v>-0.982</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1214</v>
+        <v>-1.6687</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4081</v>
+        <v>0.6867</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.7935</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-1.9838</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-3.1741</v>
       </c>
       <c r="R8" t="n">
         <v>1.1903</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2794</v>
+        <v>-0.2905</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3175</v>
+        <v>-0.5214</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5969</v>
+        <v>0.2309</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4012</v>
+        <v>-2.0757</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4012</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DIEZ VALERO</t>
+          <t>J. ESONO MBA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4331</v>
+        <v>-1.2912</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3317</v>
+        <v>-0.7422</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1014</v>
+        <v>-0.5491</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.019</v>
+        <v>2.645</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.492</v>
+        <v>2.0762</v>
       </c>
       <c r="I9" t="n">
-        <v>1.473</v>
+        <v>0.5688</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3516</v>
+        <v>2.3583</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7014</v>
+        <v>2.1976</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6502</v>
+        <v>0.1606</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3706</v>
+        <v>0.2867</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.1933</v>
+        <v>-0.1214</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8227</v>
+        <v>0.4081</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5952</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1903</v>
+        <v>-3.1741</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7855</v>
+        <v>1.1903</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.5512</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.493</v>
+        <v>0.0737</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0438</v>
+        <v>-0.625</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4724</v>
+        <v>-1.4012</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4724</v>
+        <v>-1.4012</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. GARCIA IBAÑEZ</t>
+          <t>A. DIEZ VALERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5253</v>
+        <v>-1.6006</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3076</v>
+        <v>-0.2467</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8329</v>
+        <v>-1.3539</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0972</v>
+        <v>-0.019</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2804</v>
+        <v>-1.492</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3775</v>
+        <v>1.473</v>
       </c>
       <c r="J10" t="n">
-        <v>3.0792</v>
+        <v>1.3516</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3884</v>
+        <v>0.7014</v>
       </c>
       <c r="L10" t="n">
-        <v>2.6908</v>
+        <v>0.6502</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.982</v>
+        <v>-1.3706</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6687</v>
+        <v>-2.1933</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6867</v>
+        <v>0.8227</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9838</v>
+        <v>-1.1903</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1903</v>
+        <v>1.7855</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7533</v>
+        <v>-0.7043</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.408</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0345</v>
+        <v>-0.2963</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0757</v>
+        <v>-1.4724</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.0757</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0802</v>
+        <v>-3.6058</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.186</v>
+        <v>-3.8799</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1058</v>
+        <v>0.2742</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3082</v>
@@ -1312,13 +1312,13 @@
         <v>1.1903</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.772</v>
+        <v>-0.2975</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4761</v>
+        <v>-0.17</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2959</v>
+        <v>-0.1276</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4615</v>
+        <v>-4.2716</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2808</v>
+        <v>-1.8103</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1808</v>
+        <v>-2.4613</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9207</v>
@@ -1390,13 +1390,13 @@
         <v>1.7855</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7312</v>
+        <v>-0.5413</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2865</v>
+        <v>-0.8161</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5554</v>
+        <v>0.2748</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4129</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8176</v>
+        <v>-5.2209</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4727</v>
+        <v>-3.9602</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3449</v>
+        <v>-1.2608</v>
       </c>
       <c r="G13" t="n">
         <v>-0.775</v>
@@ -1468,13 +1468,13 @@
         <v>2.1822</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1639</v>
+        <v>-0.2395</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3742</v>
+        <v>-0.1133</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2104</v>
+        <v>-0.1262</v>
       </c>
       <c r="V13" t="n">
         <v>-3.0162</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.6521</v>
+        <v>-12.7171</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.1153</v>
+        <v>-4.180099999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.537099999999999</v>
+        <v>-8.536999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>2.558500000000001</v>
@@ -1522,7 +1522,7 @@
         <v>12.322</v>
       </c>
       <c r="K14" t="n">
-        <v>5.8776</v>
+        <v>5.877600000000001</v>
       </c>
       <c r="L14" t="n">
         <v>6.4442</v>
@@ -1546,13 +1546,13 @@
         <v>16.8626</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.1416</v>
+        <v>-6.206599999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.4201</v>
+        <v>-3.4852</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.7215</v>
+        <v>-2.7216</v>
       </c>
       <c r="V14" t="n">
         <v>-11.0529</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>14.7039</v>
+        <v>13.9532</v>
       </c>
       <c r="E15" t="n">
-        <v>12.3734</v>
+        <v>11.6592</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3305</v>
+        <v>2.294</v>
       </c>
       <c r="G15" t="n">
         <v>6.27</v>
@@ -1624,13 +1624,13 @@
         <v>1.7855</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5999</v>
+        <v>1.8492</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1168</v>
+        <v>0.4026</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4832</v>
+        <v>1.4467</v>
       </c>
       <c r="V15" t="n">
         <v>6.0323</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.8573</v>
+        <v>5.775</v>
       </c>
       <c r="E16" t="n">
-        <v>4.565</v>
+        <v>3.2386</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2924</v>
+        <v>2.5364</v>
       </c>
       <c r="G16" t="n">
         <v>0.161</v>
@@ -1702,13 +1702,13 @@
         <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8947</v>
+        <v>1.8124</v>
       </c>
       <c r="T16" t="n">
-        <v>1.984</v>
+        <v>0.6576</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9107</v>
+        <v>1.1547</v>
       </c>
       <c r="V16" t="n">
         <v>2.4129</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5385</v>
+        <v>2.3148</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5683</v>
+        <v>1.1805</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9702</v>
+        <v>1.1343</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7282999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>1.7855</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2137</v>
+        <v>0.5625</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.238</v>
+        <v>0.3741</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0243</v>
+        <v>0.1884</v>
       </c>
       <c r="V17" t="n">
         <v>2.6789</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4512</v>
+        <v>0.7149</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0504</v>
+        <v>1.2341</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5992</v>
+        <v>-0.5192</v>
       </c>
       <c r="G18" t="n">
         <v>-0.352</v>
@@ -1858,13 +1858,13 @@
         <v>1.9838</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9464</v>
+        <v>1.2101</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4285</v>
+        <v>0.6122</v>
       </c>
       <c r="U18" t="n">
-        <v>0.518</v>
+        <v>0.5979</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1352</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. NGOMO MIFUMU</t>
+          <t>I. OLLE GATELL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.865</v>
+        <v>0.3521</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.0227</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7375</v>
+        <v>0.3747</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5403</v>
+        <v>0.0049</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9728</v>
+        <v>-0.2672</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5131</v>
+        <v>0.2721</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0894</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6893</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5999</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6297</v>
+        <v>0.0049</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7165</v>
+        <v>-0.2672</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9133</v>
+        <v>0.2721</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7855</v>
+        <v>0.1984</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1903</v>
+        <v>0.1984</v>
       </c>
       <c r="S19" t="n">
-        <v>1.647</v>
+        <v>0.1488</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1926</v>
+        <v>-0.0227</v>
       </c>
       <c r="U19" t="n">
-        <v>1.8397</v>
+        <v>0.1714</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5437</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. OLLE GATELL</t>
+          <t>O. NGOMO MIFUMU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3342</v>
+        <v>0.3515</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1247</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4589</v>
+        <v>1.224</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0049</v>
+        <v>-0.5403</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2672</v>
+        <v>0.9728</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2721</v>
+        <v>-1.5131</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.0894</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1.6893</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.5999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0049</v>
+        <v>-1.6297</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2672</v>
+        <v>-0.7165</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2721</v>
+        <v>-0.9133</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1984</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1309</v>
+        <v>1.1336</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1247</v>
+        <v>-0.1926</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2556</v>
+        <v>1.3262</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.5437</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4245</v>
+        <v>-0.5283</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2583</v>
+        <v>-0.6664</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1662</v>
+        <v>0.1382</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1745</v>
@@ -2092,13 +2092,13 @@
         <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8888</v>
+        <v>0.7851</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1224</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2336</v>
+        <v>0.0708</v>
       </c>
       <c r="V21" t="n">
         <v>0.266</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ROSA BEJARANO</t>
+          <t>O. BESORA TOMAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.023</v>
+        <v>-0.7839</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2435</v>
+        <v>-2.6301</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2205</v>
+        <v>1.8462</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7733</v>
+        <v>-1.544</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6505</v>
+        <v>0.6999</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4238</v>
+        <v>-2.2439</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2711</v>
+        <v>-0.8779</v>
       </c>
       <c r="K22" t="n">
-        <v>2.5913</v>
+        <v>1.2755</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3202</v>
+        <v>-2.1534</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0443</v>
+        <v>-0.6661</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.9408</v>
+        <v>-0.5755</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1035</v>
+        <v>-0.0905</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.9758</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7855</v>
+        <v>1.9838</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3491</v>
+        <v>0.5456</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1303</v>
+        <v>0.0171</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4794</v>
+        <v>0.5284</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.4085</v>
+        <v>1.2065</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.4085</v>
+        <v>1.2065</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O. BESORA TOMAS</t>
+          <t>A. ROSA BEJARANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.332</v>
+        <v>-1.6012</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9565</v>
+        <v>-1.7334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.1321</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.544</v>
+        <v>-0.7733</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6999</v>
+        <v>0.6505</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.2439</v>
+        <v>-1.4238</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8779</v>
+        <v>1.2711</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2755</v>
+        <v>2.5913</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.1534</v>
+        <v>-1.3202</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6661</v>
+        <v>-2.0443</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5755</v>
+        <v>-1.9408</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0905</v>
+        <v>-0.1035</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.9758</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9838</v>
+        <v>1.7855</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0025</v>
+        <v>0.7709</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3092</v>
+        <v>0.3799</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6933</v>
+        <v>0.391</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2065</v>
+        <v>-0.4085</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2065</v>
+        <v>-0.4085</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.3183</v>
+        <v>-4.8551</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5644</v>
+        <v>-2.8502</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7539</v>
+        <v>-2.0049</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8821</v>
@@ -2326,13 +2326,13 @@
         <v>1.1903</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.099</v>
+        <v>0.3642</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9352</v>
+        <v>-0.221</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1639</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5437</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>13.6523</v>
+        <v>15.693</v>
       </c>
       <c r="E25" t="n">
-        <v>8.537200000000002</v>
+        <v>8.537099999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>5.115200000000001</v>
+        <v>7.1558</v>
       </c>
       <c r="G25" t="n">
         <v>-2.5586</v>
@@ -2377,7 +2377,7 @@
         <v>-11.3031</v>
       </c>
       <c r="J25" t="n">
-        <v>9.763399999999999</v>
+        <v>9.763400000000001</v>
       </c>
       <c r="K25" t="n">
         <v>14.6223</v>
@@ -2392,7 +2392,7 @@
         <v>-5.8775</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.444299999999999</v>
+        <v>-6.4443</v>
       </c>
       <c r="P25" t="n">
         <v>-1.9838</v>
@@ -2404,13 +2404,13 @@
         <v>14.8789</v>
       </c>
       <c r="S25" t="n">
-        <v>7.1416</v>
+        <v>9.182399999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7217</v>
+        <v>2.7214</v>
       </c>
       <c r="U25" t="n">
-        <v>4.420100000000001</v>
+        <v>6.4607</v>
       </c>
       <c r="V25" t="n">
         <v>11.0529</v>
